--- a/Data/Export/Common/ItemType_道具类型.xlsx
+++ b/Data/Export/Common/ItemType_道具类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB73BBA-F280-455E-9F70-AE78DF47A80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7059D9-89A7-41AF-8970-0DC71F319B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemTypes" sheetId="36" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="128">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -316,6 +316,189 @@
   </si>
   <si>
     <t>戟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤兔马</t>
+  </si>
+  <si>
+    <t>的卢</t>
+  </si>
+  <si>
+    <t>爪黄飞电</t>
+  </si>
+  <si>
+    <t>绝影</t>
+  </si>
+  <si>
+    <t>大宛马</t>
+  </si>
+  <si>
+    <t>七星宝刀</t>
+  </si>
+  <si>
+    <t>倚天剑</t>
+  </si>
+  <si>
+    <t>青釭剑</t>
+  </si>
+  <si>
+    <t>雌雄一对剑</t>
+  </si>
+  <si>
+    <t>方天画戟</t>
+  </si>
+  <si>
+    <t>青龙偃月刀</t>
+  </si>
+  <si>
+    <t>蛇矛</t>
+  </si>
+  <si>
+    <t>流星锤</t>
+  </si>
+  <si>
+    <t>飞刀</t>
+  </si>
+  <si>
+    <t>短戟</t>
+  </si>
+  <si>
+    <t>手戟</t>
+  </si>
+  <si>
+    <t>铁锁</t>
+  </si>
+  <si>
+    <t>养由基弓</t>
+  </si>
+  <si>
+    <t>李广弓</t>
+  </si>
+  <si>
+    <t>檀弓</t>
+  </si>
+  <si>
+    <t>东胡飞弓</t>
+  </si>
+  <si>
+    <t>貊弓</t>
+  </si>
+  <si>
+    <t>孙子兵法</t>
+  </si>
+  <si>
+    <t>兵法二十四篇</t>
+  </si>
+  <si>
+    <t>孟德新书</t>
+  </si>
+  <si>
+    <t>六韬</t>
+  </si>
+  <si>
+    <t>三略</t>
+  </si>
+  <si>
+    <t>吴子</t>
+  </si>
+  <si>
+    <t>尉缭子</t>
+  </si>
+  <si>
+    <t>战国策</t>
+  </si>
+  <si>
+    <t>司马法</t>
+  </si>
+  <si>
+    <t>墨子</t>
+  </si>
+  <si>
+    <t>太平要术</t>
+  </si>
+  <si>
+    <t>玉玺</t>
+  </si>
+  <si>
+    <t>铜雀</t>
+  </si>
+  <si>
+    <t>subKind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陷阵营兵符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虎卫军兵符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>藤甲兵兵符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青州兵兵符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白毦兵兵符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大戟士兵符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虎豹骑兵符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白马义从兵符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>西凉铁骑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兵符</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>象兵兵符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无当飞军兵符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锦帆军兵符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -323,7 +506,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,6 +561,13 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="1"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -819,32 +1009,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
-  <dimension ref="A1:AD69"/>
+  <dimension ref="A1:AE71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="2" customWidth="1"/>
-    <col min="6" max="7" width="9.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="54.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="21.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="8.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="9.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="2" customWidth="1"/>
+    <col min="7" max="8" width="9.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="54.625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="15.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:31" s="9" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11"/>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -855,36 +1046,36 @@
       <c r="D1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="13"/>
+      <c r="F1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="17"/>
       <c r="G1" s="17"/>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="17"/>
+      <c r="I1" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="13"/>
       <c r="Q1" s="13"/>
       <c r="R1" s="13"/>
       <c r="S1" s="13"/>
@@ -893,14 +1084,15 @@
       <c r="V1" s="13"/>
       <c r="W1" s="13"/>
       <c r="X1" s="13"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="6"/>
-    </row>
-    <row r="2" spans="1:30" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="8"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="8"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="6"/>
+    </row>
+    <row r="2" spans="1:31" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -908,19 +1100,19 @@
       <c r="C2" s="2"/>
       <c r="D2"/>
       <c r="E2"/>
-      <c r="F2" s="18"/>
+      <c r="F2"/>
       <c r="G2" s="18"/>
-      <c r="H2"/>
+      <c r="H2" s="18"/>
       <c r="I2"/>
       <c r="J2"/>
-      <c r="K2" s="2"/>
+      <c r="K2"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="2"/>
+      <c r="N2" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="14"/>
+      <c r="P2" s="2"/>
       <c r="Q2" s="14"/>
       <c r="R2" s="14"/>
       <c r="S2" s="14"/>
@@ -929,14 +1121,15 @@
       <c r="V2" s="14"/>
       <c r="W2" s="14"/>
       <c r="X2" s="14"/>
-      <c r="Y2" s="2"/>
+      <c r="Y2" s="14"/>
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
-    </row>
-    <row r="3" spans="1:30" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE2" s="2"/>
+    </row>
+    <row r="3" spans="1:31" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -950,39 +1143,41 @@
         <v>14</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="L3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
@@ -997,8 +1192,9 @@
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
       <c r="AD3" s="7"/>
-    </row>
-    <row r="4" spans="1:30" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AE3" s="7"/>
+    </row>
+    <row r="4" spans="1:31" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -1015,26 +1211,26 @@
         <v>13</v>
       </c>
       <c r="F4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>5</v>
-      </c>
       <c r="H4" s="16" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="K4" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="L4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="16" t="s">
-        <v>5</v>
-      </c>
       <c r="M4" s="16" t="s">
         <v>5</v>
       </c>
@@ -1044,7 +1240,9 @@
       <c r="O4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="P4" s="15"/>
+      <c r="P4" s="16" t="s">
+        <v>5</v>
+      </c>
       <c r="Q4" s="15"/>
       <c r="R4" s="15"/>
       <c r="S4" s="15"/>
@@ -1053,8 +1251,9 @@
       <c r="V4" s="15"/>
       <c r="W4" s="15"/>
       <c r="X4" s="15"/>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="Y4" s="15"/>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -1065,23 +1264,25 @@
         <v>0</v>
       </c>
       <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4" t="s">
+      <c r="G5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="4"/>
+      <c r="L5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
@@ -1093,9 +1294,10 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
-      <c r="AC5" s="4"/>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="AB5" s="4"/>
+      <c r="AD5" s="4"/>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -1107,25 +1309,27 @@
         <v>1</v>
       </c>
       <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4">
         <v>2</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="4"/>
+      <c r="J6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <v>35</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
@@ -1137,9 +1341,10 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
-      <c r="AC6" s="4"/>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="AB6" s="4"/>
+      <c r="AD6" s="4"/>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -1150,25 +1355,27 @@
         <v>1</v>
       </c>
       <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
         <v>3</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="4">
+      <c r="K7" s="4">
         <v>35</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
@@ -1180,9 +1387,10 @@
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
-      <c r="AC7" s="4"/>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="AB7" s="4"/>
+      <c r="AD7" s="4"/>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.15">
       <c r="B8" s="4">
         <v>4</v>
       </c>
@@ -1193,25 +1401,27 @@
         <v>1</v>
       </c>
       <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="4">
         <v>35</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
@@ -1223,9 +1433,10 @@
       <c r="Y8" s="4"/>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
-      <c r="AC8" s="4"/>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="AB8" s="4"/>
+      <c r="AD8" s="4"/>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -1236,25 +1447,27 @@
         <v>2</v>
       </c>
       <c r="E9" s="4">
-        <v>5</v>
-      </c>
-      <c r="F9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4">
+        <v>5</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="4">
+      <c r="K9" s="4">
         <v>36</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
@@ -1266,9 +1479,10 @@
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
-      <c r="AC9" s="4"/>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="AB9" s="4"/>
+      <c r="AD9" s="4"/>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -1279,31 +1493,33 @@
         <v>3</v>
       </c>
       <c r="E10" s="4">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4">
         <v>6</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="4"/>
+      <c r="J10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="4">
+      <c r="K10" s="4">
         <v>37</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
@@ -1315,9 +1531,10 @@
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
       <c r="AA10" s="4"/>
-      <c r="AC10" s="4"/>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="AB10" s="4"/>
+      <c r="AD10" s="4"/>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -1328,30 +1545,32 @@
         <v>3</v>
       </c>
       <c r="E11" s="4">
+        <v>3</v>
+      </c>
+      <c r="F11" s="4">
         <v>6</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4">
         <v>1</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="J11" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="4">
+      <c r="K11" s="4">
         <v>37</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
@@ -1363,9 +1582,10 @@
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
-      <c r="AC11" s="4"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="AB11" s="4"/>
+      <c r="AD11" s="4"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -1376,31 +1596,33 @@
         <v>3</v>
       </c>
       <c r="E12" s="4">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4">
         <v>7</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="4"/>
+      <c r="J12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="4">
+      <c r="K12" s="4">
         <v>37</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
@@ -1412,9 +1634,10 @@
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
-      <c r="AC12" s="4"/>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="AB12" s="4"/>
+      <c r="AD12" s="4"/>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -1425,30 +1648,32 @@
         <v>3</v>
       </c>
       <c r="E13" s="4">
+        <v>3</v>
+      </c>
+      <c r="F13" s="4">
         <v>7</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="4">
+      <c r="I13" s="4">
         <v>2</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="J13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="4">
+      <c r="K13" s="4">
         <v>37</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
@@ -1460,9 +1685,10 @@
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
-      <c r="AC13" s="4"/>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="AB13" s="4"/>
+      <c r="AD13" s="4"/>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -1473,23 +1699,25 @@
         <v>4</v>
       </c>
       <c r="E14" s="4">
+        <v>4</v>
+      </c>
+      <c r="F14" s="4">
         <v>8</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4" t="s">
+      <c r="G14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="4"/>
+      <c r="L14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
@@ -1501,9 +1729,10 @@
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
-      <c r="AC14" s="4"/>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="AB14" s="4"/>
+      <c r="AD14" s="4"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -1514,31 +1743,33 @@
         <v>4</v>
       </c>
       <c r="E15" s="4">
+        <v>4</v>
+      </c>
+      <c r="F15" s="4">
         <v>8</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J15" s="4">
+      <c r="K15" s="4">
         <v>38</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
@@ -1550,9 +1781,10 @@
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
-      <c r="AC15" s="4"/>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="AB15" s="4"/>
+      <c r="AD15" s="4"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -1563,30 +1795,32 @@
         <v>4</v>
       </c>
       <c r="E16" s="4">
+        <v>4</v>
+      </c>
+      <c r="F16" s="4">
         <v>8</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H16" s="4">
+      <c r="I16" s="4">
         <v>2</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="4">
+      <c r="K16" s="4">
         <v>38</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
@@ -1598,17 +1832,39 @@
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
-      <c r="AC16" s="4"/>
-    </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="AB16" s="4"/>
+      <c r="AD16" s="4"/>
+    </row>
+    <row r="17" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B17" s="4">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="4">
+        <v>8</v>
+      </c>
+      <c r="F17" s="4">
+        <v>13</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
-      <c r="P17" s="4"/>
+      <c r="K17" s="4">
+        <v>51</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
@@ -1620,17 +1876,31 @@
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
-      <c r="AC17" s="4"/>
-    </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="AB17" s="4"/>
+      <c r="AD17" s="4"/>
+    </row>
+    <row r="18" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B18" s="4">
+        <v>14</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E18" s="4">
+        <v>8</v>
+      </c>
+      <c r="F18" s="4">
+        <v>14</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
-      <c r="P18" s="4"/>
+      <c r="K18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
@@ -1642,510 +1912,1330 @@
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
-      <c r="AC18" s="4"/>
-    </row>
-    <row r="19" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="AB18" s="4"/>
+      <c r="AD18" s="4"/>
+    </row>
+    <row r="19" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B19" s="4">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" s="4">
+        <v>8</v>
+      </c>
+      <c r="F19" s="4">
+        <v>15</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
-      <c r="Y19" s="4"/>
+      <c r="K19" s="4"/>
       <c r="Z19" s="4"/>
       <c r="AA19" s="4"/>
-      <c r="AC19" s="4"/>
-    </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="AB19" s="4"/>
+      <c r="AD19" s="4"/>
+    </row>
+    <row r="20" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B20" s="4">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="4">
+        <v>8</v>
+      </c>
+      <c r="F20" s="4">
+        <v>16</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-      <c r="Y20" s="4"/>
+      <c r="K20" s="4"/>
       <c r="Z20" s="4"/>
       <c r="AA20" s="4"/>
-      <c r="AC20" s="4"/>
-    </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="AB20" s="4"/>
+      <c r="AD20" s="4"/>
+    </row>
+    <row r="21" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B21" s="4">
+        <v>17</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" s="4">
+        <v>8</v>
+      </c>
+      <c r="F21" s="4">
+        <v>17</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
-      <c r="Y21" s="4"/>
+      <c r="K21" s="4"/>
       <c r="Z21" s="4"/>
       <c r="AA21" s="4"/>
-      <c r="AC21" s="4"/>
-    </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="AB21" s="4"/>
+      <c r="AD21" s="4"/>
+    </row>
+    <row r="22" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B22" s="4">
+        <v>18</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" s="4">
+        <v>8</v>
+      </c>
+      <c r="F22" s="4">
+        <v>18</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
-      <c r="Y22" s="4"/>
+      <c r="K22" s="4"/>
       <c r="Z22" s="4"/>
       <c r="AA22" s="4"/>
-      <c r="AC22" s="4"/>
-    </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="AB22" s="4"/>
+      <c r="AD22" s="4"/>
+    </row>
+    <row r="23" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B23" s="4">
+        <v>19</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" s="4">
+        <v>8</v>
+      </c>
+      <c r="F23" s="4">
+        <v>19</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
-      <c r="Y23" s="4"/>
+      <c r="K23" s="4"/>
       <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
-      <c r="AC23" s="4"/>
-    </row>
-    <row r="24" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="AB23" s="4"/>
+      <c r="AD23" s="4"/>
+    </row>
+    <row r="24" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B24" s="4">
+        <v>20</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" s="4">
+        <v>8</v>
+      </c>
+      <c r="F24" s="4">
+        <v>20</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
-      <c r="Y24" s="4"/>
+      <c r="K24" s="4"/>
       <c r="Z24" s="4"/>
       <c r="AA24" s="4"/>
-      <c r="AC24" s="4"/>
-    </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="AB24" s="4"/>
+      <c r="AD24" s="4"/>
+    </row>
+    <row r="25" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B25" s="4">
+        <v>21</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="4">
+        <v>8</v>
+      </c>
+      <c r="F25" s="4">
+        <v>21</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
-      <c r="Y25" s="4"/>
+      <c r="K25" s="4"/>
       <c r="Z25" s="4"/>
       <c r="AA25" s="4"/>
-      <c r="AC25" s="4"/>
-    </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="AB25" s="4"/>
+      <c r="AD25" s="4"/>
+    </row>
+    <row r="26" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B26" s="4">
+        <v>22</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E26" s="4">
+        <v>8</v>
+      </c>
+      <c r="F26" s="4">
+        <v>22</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
-      <c r="Y26" s="4"/>
+      <c r="K26" s="4"/>
       <c r="Z26" s="4"/>
       <c r="AA26" s="4"/>
-      <c r="AC26" s="4"/>
-    </row>
-    <row r="27" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="H27" s="4"/>
+      <c r="AB26" s="4"/>
+      <c r="AD26" s="4"/>
+    </row>
+    <row r="27" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B27" s="4">
+        <v>23</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" s="4">
+        <v>8</v>
+      </c>
+      <c r="F27" s="4">
+        <v>23</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-      <c r="Y27" s="4"/>
+      <c r="K27" s="4"/>
       <c r="Z27" s="4"/>
       <c r="AA27" s="4"/>
-      <c r="AC27" s="4"/>
-    </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="AB27" s="4"/>
+      <c r="AD27" s="4"/>
+    </row>
+    <row r="28" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B28" s="4">
+        <v>24</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" s="4">
+        <v>8</v>
+      </c>
+      <c r="F28" s="4">
+        <v>24</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-      <c r="Y28" s="4"/>
+      <c r="K28" s="4"/>
       <c r="Z28" s="4"/>
       <c r="AA28" s="4"/>
-      <c r="AC28" s="4"/>
-    </row>
-    <row r="29" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="AB28" s="4"/>
+      <c r="AD28" s="4"/>
+    </row>
+    <row r="29" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B29" s="4">
+        <v>25</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="4">
+        <v>5</v>
+      </c>
+      <c r="E29" s="4">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4">
+        <v>25</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-      <c r="Y29" s="4"/>
+      <c r="K29" s="4"/>
       <c r="Z29" s="4"/>
       <c r="AA29" s="4"/>
-      <c r="AC29" s="4"/>
-    </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="AB29" s="4"/>
+      <c r="AD29" s="4"/>
+    </row>
+    <row r="30" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B30" s="4">
+        <v>26</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="4">
+        <v>5</v>
+      </c>
+      <c r="E30" s="4">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4">
+        <v>26</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-      <c r="Y30" s="4"/>
+      <c r="K30" s="4"/>
       <c r="Z30" s="4"/>
       <c r="AA30" s="4"/>
-      <c r="AC30" s="4"/>
-    </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="AB30" s="4"/>
+      <c r="AD30" s="4"/>
+    </row>
+    <row r="31" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B31" s="4">
+        <v>27</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="4">
+        <v>5</v>
+      </c>
+      <c r="E31" s="4">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4">
+        <v>27</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
-      <c r="Y31" s="4"/>
+      <c r="K31" s="4"/>
       <c r="Z31" s="4"/>
       <c r="AA31" s="4"/>
-      <c r="AC31" s="4"/>
-    </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="AB31" s="4"/>
+      <c r="AD31" s="4"/>
+    </row>
+    <row r="32" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B32" s="4">
+        <v>28</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="4">
+        <v>5</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4">
+        <v>28</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
-      <c r="Y32" s="4"/>
+      <c r="K32" s="4"/>
       <c r="Z32" s="4"/>
       <c r="AA32" s="4"/>
-      <c r="AC32" s="4"/>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="AB32" s="4"/>
+      <c r="AD32" s="4"/>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B33" s="4">
+        <v>29</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="4">
+        <v>5</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4">
+        <v>29</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
-      <c r="Y33" s="4"/>
+      <c r="K33" s="4"/>
       <c r="Z33" s="4"/>
       <c r="AA33" s="4"/>
-      <c r="AC33" s="4"/>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="AB33" s="4"/>
+      <c r="AD33" s="4"/>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B34" s="4">
+        <v>30</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="4">
+        <v>5</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4">
+        <v>30</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
-      <c r="Y34" s="4"/>
+      <c r="K34" s="4"/>
       <c r="Z34" s="4"/>
       <c r="AA34" s="4"/>
-      <c r="AC34" s="4"/>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="AB34" s="4"/>
+      <c r="AD34" s="4"/>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B35" s="4">
+        <v>31</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="4">
+        <v>5</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4">
+        <v>31</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
-      <c r="Y35" s="4"/>
+      <c r="K35" s="4"/>
       <c r="Z35" s="4"/>
       <c r="AA35" s="4"/>
-      <c r="AC35" s="4"/>
-    </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="AB35" s="4"/>
+      <c r="AD35" s="4"/>
+    </row>
+    <row r="36" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B36" s="4">
+        <v>32</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" s="4">
+        <v>5</v>
+      </c>
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4">
+        <v>32</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
-      <c r="Y36" s="4"/>
+      <c r="K36" s="4"/>
       <c r="Z36" s="4"/>
       <c r="AA36" s="4"/>
-      <c r="AC36" s="4"/>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="B37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="AB36" s="4"/>
+      <c r="AD36" s="4"/>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B37" s="4">
+        <v>33</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="4">
+        <v>5</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4">
+        <v>33</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
-      <c r="Y37" s="4"/>
+      <c r="K37" s="4"/>
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
-      <c r="AC37" s="4"/>
-    </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="AB37" s="4"/>
+      <c r="AD37" s="4"/>
+    </row>
+    <row r="38" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B38" s="4">
+        <v>34</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="4">
+        <v>5</v>
+      </c>
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4">
+        <v>34</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
-      <c r="Y38" s="4"/>
+      <c r="K38" s="4"/>
       <c r="Z38" s="4"/>
       <c r="AA38" s="4"/>
-      <c r="AC38" s="4"/>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="AB38" s="4"/>
+      <c r="AD38" s="4"/>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B39" s="4">
+        <v>35</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D39" s="4">
+        <v>5</v>
+      </c>
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4">
+        <v>35</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
-      <c r="Y39" s="4"/>
+      <c r="K39" s="4"/>
       <c r="Z39" s="4"/>
       <c r="AA39" s="4"/>
-      <c r="AC39" s="4"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="H40" s="4"/>
+      <c r="AB39" s="4"/>
+      <c r="AD39" s="4"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B40" s="4">
+        <v>36</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="4">
+        <v>5</v>
+      </c>
+      <c r="E40" s="4">
+        <v>2</v>
+      </c>
+      <c r="F40" s="4">
+        <v>36</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
-      <c r="Y40" s="4"/>
+      <c r="K40" s="4"/>
       <c r="Z40" s="4"/>
       <c r="AA40" s="4"/>
-      <c r="AC40" s="4"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="H41" s="4"/>
+      <c r="AB40" s="4"/>
+      <c r="AD40" s="4"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B41" s="4">
+        <v>37</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="4">
+        <v>5</v>
+      </c>
+      <c r="E41" s="4">
+        <v>2</v>
+      </c>
+      <c r="F41" s="4">
+        <v>37</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
-      <c r="Y41" s="4"/>
+      <c r="K41" s="4"/>
       <c r="Z41" s="4"/>
       <c r="AA41" s="4"/>
-      <c r="AC41" s="4"/>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="H42" s="4"/>
+      <c r="AB41" s="4"/>
+      <c r="AD41" s="4"/>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B42" s="4">
+        <v>38</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" s="4">
+        <v>5</v>
+      </c>
+      <c r="E42" s="4">
+        <v>2</v>
+      </c>
+      <c r="F42" s="4">
+        <v>38</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
-      <c r="Y42" s="4"/>
+      <c r="K42" s="4"/>
       <c r="Z42" s="4"/>
       <c r="AA42" s="4"/>
-      <c r="AC42" s="4"/>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="H43" s="4"/>
+      <c r="AB42" s="4"/>
+      <c r="AD42" s="4"/>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B43" s="4">
+        <v>39</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="4">
+        <v>5</v>
+      </c>
+      <c r="E43" s="4">
+        <v>3</v>
+      </c>
+      <c r="F43" s="4">
+        <v>39</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
-      <c r="Y43" s="4"/>
+      <c r="K43" s="4"/>
       <c r="Z43" s="4"/>
       <c r="AA43" s="4"/>
-      <c r="AC43" s="4"/>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="H44" s="4"/>
+      <c r="AB43" s="4"/>
+      <c r="AD43" s="4"/>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B44" s="4">
+        <v>40</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="4">
+        <v>5</v>
+      </c>
+      <c r="E44" s="4">
+        <v>3</v>
+      </c>
+      <c r="F44" s="4">
+        <v>40</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
-      <c r="Y44" s="4"/>
+      <c r="K44" s="4"/>
       <c r="Z44" s="4"/>
       <c r="AA44" s="4"/>
-      <c r="AC44" s="4"/>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="H45" s="4"/>
+      <c r="AB44" s="4"/>
+      <c r="AD44" s="4"/>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B45" s="4">
+        <v>41</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="4">
+        <v>5</v>
+      </c>
+      <c r="E45" s="4">
+        <v>3</v>
+      </c>
+      <c r="F45" s="4">
+        <v>41</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
-      <c r="Y45" s="4"/>
+      <c r="K45" s="4"/>
       <c r="Z45" s="4"/>
       <c r="AA45" s="4"/>
-      <c r="AC45" s="4"/>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="H46" s="4"/>
+      <c r="AB45" s="4"/>
+      <c r="AD45" s="4"/>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B46" s="4">
+        <v>42</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="4">
+        <v>5</v>
+      </c>
+      <c r="E46" s="4">
+        <v>3</v>
+      </c>
+      <c r="F46" s="4">
+        <v>42</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
-      <c r="Y46" s="4"/>
-      <c r="AA46" s="4"/>
-      <c r="AC46" s="4"/>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="H47" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="Z46" s="4"/>
+      <c r="AB46" s="4"/>
+      <c r="AD46" s="4"/>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B47" s="4">
+        <v>43</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D47" s="4">
+        <v>5</v>
+      </c>
+      <c r="E47" s="4">
+        <v>3</v>
+      </c>
+      <c r="F47" s="4">
+        <v>43</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.15">
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="H48" s="4"/>
+      <c r="K47" s="4"/>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.15">
+      <c r="B48" s="4">
+        <v>44</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="4">
+        <v>5</v>
+      </c>
+      <c r="E48" s="4">
+        <v>3</v>
+      </c>
+      <c r="F48" s="4">
+        <v>44</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
-    </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="H49" s="4"/>
+      <c r="K48" s="4"/>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B49" s="4">
+        <v>45</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D49" s="4">
+        <v>5</v>
+      </c>
+      <c r="E49" s="4">
+        <v>3</v>
+      </c>
+      <c r="F49" s="4">
+        <v>45</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
-    </row>
-    <row r="50" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="H50" s="4"/>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B50" s="4">
+        <v>46</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" s="4">
+        <v>5</v>
+      </c>
+      <c r="E50" s="4">
+        <v>3</v>
+      </c>
+      <c r="F50" s="4">
+        <v>46</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
-    </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="H51" s="4"/>
+      <c r="K50" s="4"/>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B51" s="4">
+        <v>47</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D51" s="4">
+        <v>5</v>
+      </c>
+      <c r="E51" s="4">
+        <v>4</v>
+      </c>
+      <c r="F51" s="4">
+        <v>47</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
-    </row>
-    <row r="52" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="H52" s="4"/>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B52" s="4">
+        <v>48</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D52" s="4">
+        <v>5</v>
+      </c>
+      <c r="E52" s="4">
+        <v>4</v>
+      </c>
+      <c r="F52" s="4">
+        <v>48</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
-    </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="H53" s="4"/>
+      <c r="K52" s="4"/>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B53" s="4">
+        <v>49</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="4">
+        <v>5</v>
+      </c>
+      <c r="E53" s="4">
+        <v>4</v>
+      </c>
+      <c r="F53" s="4">
+        <v>49</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
-    </row>
-    <row r="54" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="H54" s="4"/>
+      <c r="K53" s="4"/>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B54" s="4">
+        <v>50</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="4">
+        <v>5</v>
+      </c>
+      <c r="E54" s="4">
+        <v>4</v>
+      </c>
+      <c r="F54" s="4">
+        <v>50</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
-    </row>
-    <row r="55" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="H55" s="4"/>
+      <c r="K54" s="4"/>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B55" s="4">
+        <v>51</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D55" s="4">
+        <v>5</v>
+      </c>
+      <c r="E55" s="4">
+        <v>4</v>
+      </c>
+      <c r="F55" s="4">
+        <v>51</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
-    </row>
-    <row r="56" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="H56" s="4"/>
+      <c r="K55" s="4"/>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B56" s="4">
+        <v>52</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="4">
+        <v>5</v>
+      </c>
+      <c r="E56" s="4">
+        <v>4</v>
+      </c>
+      <c r="F56" s="4">
+        <v>52</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
-    </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="H57" s="4"/>
+      <c r="K56" s="4"/>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B57" s="4">
+        <v>53</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D57" s="4">
+        <v>5</v>
+      </c>
+      <c r="E57" s="4">
+        <v>4</v>
+      </c>
+      <c r="F57" s="4">
+        <v>53</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
-    </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="H58" s="4"/>
+      <c r="K57" s="4"/>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B58" s="4">
+        <v>54</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" s="4">
+        <v>5</v>
+      </c>
+      <c r="E58" s="4">
+        <v>4</v>
+      </c>
+      <c r="F58" s="4">
+        <v>54</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
-    </row>
-    <row r="59" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="H59" s="4"/>
+      <c r="K58" s="4"/>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B59" s="4">
+        <v>55</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D59" s="4">
+        <v>5</v>
+      </c>
+      <c r="E59" s="4">
+        <v>5</v>
+      </c>
+      <c r="F59" s="4">
+        <v>55</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
-    </row>
-    <row r="60" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="H60" s="4"/>
+      <c r="K59" s="4"/>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B60" s="4">
+        <v>56</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" s="4">
+        <v>5</v>
+      </c>
+      <c r="E60" s="4">
+        <v>5</v>
+      </c>
+      <c r="F60" s="4">
+        <v>56</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
-    </row>
-    <row r="61" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="H61" s="4"/>
+      <c r="K60" s="4"/>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B61" s="4">
+        <v>57</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D61" s="4">
+        <v>5</v>
+      </c>
+      <c r="E61" s="4">
+        <v>5</v>
+      </c>
+      <c r="F61" s="4">
+        <v>57</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
-    </row>
-    <row r="62" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="H62" s="4"/>
+      <c r="K61" s="4"/>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B62" s="4">
+        <v>58</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D62" s="4">
+        <v>5</v>
+      </c>
+      <c r="E62" s="4">
+        <v>5</v>
+      </c>
+      <c r="F62" s="4">
+        <v>58</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
-    </row>
-    <row r="63" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="H63" s="4"/>
+      <c r="K62" s="4"/>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B63" s="4">
+        <v>59</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="4">
+        <v>5</v>
+      </c>
+      <c r="E63" s="4">
+        <v>5</v>
+      </c>
+      <c r="F63" s="4">
+        <v>59</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
-    </row>
-    <row r="64" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="H64" s="4"/>
+      <c r="K63" s="4"/>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B64" s="4">
+        <v>60</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D64" s="4">
+        <v>5</v>
+      </c>
+      <c r="E64" s="4">
+        <v>5</v>
+      </c>
+      <c r="F64" s="4">
+        <v>60</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
-    </row>
-    <row r="65" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="H65" s="4"/>
+      <c r="K64" s="4"/>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B65" s="4">
+        <v>61</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D65" s="4">
+        <v>5</v>
+      </c>
+      <c r="E65" s="4">
+        <v>5</v>
+      </c>
+      <c r="F65" s="4">
+        <v>61</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
-    </row>
-    <row r="66" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="H66" s="4"/>
+      <c r="K65" s="4"/>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B66" s="4">
+        <v>62</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D66" s="4">
+        <v>5</v>
+      </c>
+      <c r="E66" s="4">
+        <v>5</v>
+      </c>
+      <c r="F66" s="4">
+        <v>62</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
-    </row>
-    <row r="67" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="H67" s="4"/>
+      <c r="K66" s="4"/>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B67" s="4">
+        <v>63</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D67" s="4">
+        <v>5</v>
+      </c>
+      <c r="E67" s="4">
+        <v>5</v>
+      </c>
+      <c r="F67" s="4">
+        <v>63</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
-    </row>
-    <row r="68" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="H68" s="4"/>
+      <c r="K67" s="4"/>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B68" s="4">
+        <v>64</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D68" s="4">
+        <v>5</v>
+      </c>
+      <c r="E68" s="4">
+        <v>5</v>
+      </c>
+      <c r="F68" s="4">
+        <v>64</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
-    </row>
-    <row r="69" spans="4:10" x14ac:dyDescent="0.15">
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="H69" s="4"/>
+      <c r="K68" s="4"/>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B69" s="4">
+        <v>65</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="4">
+        <v>5</v>
+      </c>
+      <c r="E69" s="4">
+        <v>5</v>
+      </c>
+      <c r="F69" s="4">
+        <v>65</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I69" s="4"/>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B70" s="4">
+        <v>66</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="4">
+        <v>5</v>
+      </c>
+      <c r="E70" s="4">
+        <v>6</v>
+      </c>
+      <c r="F70" s="4">
+        <v>66</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B71" s="4">
+        <v>67</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D71" s="4">
+        <v>5</v>
+      </c>
+      <c r="E71" s="4">
+        <v>7</v>
+      </c>
+      <c r="F71" s="4">
+        <v>67</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
